--- a/backend/backups/category1_beauty_salon_spa_FINAL.xlsx
+++ b/backend/backups/category1_beauty_salon_spa_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,187 +425,195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>38b97afd-5409-4155-835d-7d2beb1770eb</t>
+          <t>13da403a-4cc0-47de-a2d0-c2487adaef18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 1</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>24K Gold Radiance Facial</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>999</v>
+        <v>1899</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Luxurious gold-foil massage facial giving skin an instant luminous glow, firmness, and silk smoothness for special events.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional 24K Gold Radiance Facial procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete 24K Gold Radiance Facial procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.533071+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.533071+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does 24K Gold Radiance Facial take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>91c0c2d6-49a5-44ce-9684-146369687b54</t>
+          <t>232c05ef-20f1-4d9d-a120-d5a736ebc158</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 2</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>Anti-Aging Collagen Lift Facial</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>999</v>
+        <v>1999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Tightening peptide and collagen facial massaged with ice globes to diminish wrinkles and uplift sagging facial contours.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Anti-Aging Collagen Lift Facial procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Anti-Aging Collagen Lift Facial procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.537730+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.537730+00:00</t>
+          <t>[{'answer': 'The session typically takes around 75 minutes.', 'question': 'How long does Anti-Aging Collagen Lift Facial take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8652e4b8-384f-423e-800a-8dcd7695ba66</t>
+          <t>1616f5dc-dc4e-43f9-ac13-d8a3ea223e65</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 3</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>Charcoal Detox &amp; Acne Cleanup</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -630,349 +621,384 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Activated bamboo charcoal vacuum cleanup targeting stubborn blackheads, excess sebum, and active acne breakouts.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Charcoal Detox &amp; Acne Cleanup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Charcoal Detox &amp; Acne Cleanup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.541928+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.541928+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Charcoal Detox &amp; Acne Cleanup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5f153195-922b-44e8-b530-55dd22c71cbd</t>
+          <t>171399b9-5994-4904-8a3f-0c53cf8e8b66</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 4</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>Diamond Micro-Dermabrasion Facial</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>999</v>
+        <v>2499</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Precision diamond-tip exfoliation reducing acne scars, fine lines, and hyper-pigmentation for youthful skin texture.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Diamond Micro-Dermabrasion Facial procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Diamond Micro-Dermabrasion Facial procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.546520+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.546520+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Diamond Micro-Dermabrasion Facial take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3f55d2dc-3fb4-48b4-b100-c1d48359928d</t>
+          <t>025596b2-00b4-490d-9934-19aa2b5e2230</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 5</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>Fruit Glow &amp; Hydration Facial</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Nourishing organic fruit extract facial designed to deeply hydrate, exfoliate, and restore natural skin radiance.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Fruit Glow &amp; Hydration Facial procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Fruit Glow &amp; Hydration Facial procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.549243+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.549243+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Fruit Glow &amp; Hydration Facial take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16d76fe0-31a0-4c61-8edc-64dddb3f3673</t>
+          <t>11eb47da-b142-4b69-9f4e-3507846809cb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 6</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>Hydra-Facial Deep Pore Cleansing</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>999</v>
+        <v>2199</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Advanced multi-step hydro-dermabrasion treatment extracting impurities while infusing skin with hyaluronic acid serums.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Hydra-Facial Deep Pore Cleansing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Hydra-Facial Deep Pore Cleansing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.551619+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.551619+00:00</t>
+          <t>[{'answer': 'The session typically takes around 75 minutes.', 'question': 'How long does Hydra-Facial Deep Pore Cleansing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7420713a-26c1-49d8-9ddc-53aa56b9d992</t>
+          <t>0b139dae-129b-4996-bbdc-dd01d05b43a9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 7</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>O3+ Anti-Tan Brightening Facial</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>999</v>
+        <v>1499</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Professional dermatologically tested facial pack that lightens sun tan, even out skin tone, and boosts collagen synthesis.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 7 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional O3+ Anti-Tan Brightening Facial procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 7 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 7 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 7 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 7 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete O3+ Anti-Tan Brightening Facial procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.555142+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.555142+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does O3+ Anti-Tan Brightening Facial take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fc4d47f1-85e3-4aea-9108-99e66f6528f5</t>
+          <t>164353c2-9cbf-404e-b2e7-22064e69839e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 8</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>Organic Herbal De-Tan Cleanup</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Gentle herbal pack with sandalwood and aloe vera to instantly soothe sun-burned skin and remove light pigmentation.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 8 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Organic Herbal De-Tan Cleanup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 8 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 8 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 8 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 8 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Organic Herbal De-Tan Cleanup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.557923+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.557923+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Organic Herbal De-Tan Cleanup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>253b8e09-d3b9-4584-916b-bbdd3db67cd3</t>
+          <t>16d76fe0-31a0-4c61-8edc-64dddb3f3673</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare Service Variation 9</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Facial &amp; Skincare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Facial &amp; Skincare</t>
+          <t>Oxygen Bleach &amp; Face Radiance</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Mild oxygenated facial bleach that lightens facial hair to match skin tone while providing an instant bright complexion.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Complete Facial &amp; Skincare Service Variation 9 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Oxygen Bleach &amp; Face Radiance procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Facial &amp; Skincare Service Variation 9 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Facial &amp; Skincare experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Facial &amp; Skincare Service Variation 9 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Facial &amp; Skincare tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Facial &amp; Skincare Service Variation 9 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Facial &amp; Skincare Service Variation 9 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Oxygen Bleach &amp; Face Radiance procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.560516+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.560516+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Oxygen Bleach &amp; Face Radiance take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6919731b-5173-4307-a782-aca8d6de9579</t>
+          <t>41cd6220-be9a-456d-9bc8-9f05dc825aa6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling Service Variation 1</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Makeup &amp; Styling</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling</t>
+          <t>Express Eye &amp; Face Touchup Makeup</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -980,1649 +1006,1814 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Quick 30-minute touchup covering eye liner, mascara, subtle blush, and lipstick refresh for instant readiness.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Complete Makeup &amp; Styling Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Express Eye &amp; Face Touchup Makeup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Makeup &amp; Styling Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Makeup &amp; Styling experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Makeup &amp; Styling Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Makeup &amp; Styling tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Makeup &amp; Styling Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Makeup &amp; Styling Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Express Eye &amp; Face Touchup Makeup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.562974+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.562974+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Express Eye &amp; Face Touchup Makeup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>232c05ef-20f1-4d9d-a120-d5a736ebc158</t>
+          <t>2f23b287-8643-4101-b81d-501a260e8f8e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling Service Variation 2</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Makeup &amp; Styling</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling</t>
+          <t>HD Flawless Bridal Makeup Package</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>999</v>
+        <v>9999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>High-definition camera-ready bridal makeover with waterproof base, contouring, hair styling, and jewelry setting.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Complete Makeup &amp; Styling Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional HD Flawless Bridal Makeup Package procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Makeup &amp; Styling Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Makeup &amp; Styling experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Makeup &amp; Styling Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Makeup &amp; Styling tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Makeup &amp; Styling Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Makeup &amp; Styling Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete HD Flawless Bridal Makeup Package procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.565510+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.565510+00:00</t>
+          <t>[{'answer': 'The session typically takes around 180 minutes.', 'question': 'How long does HD Flawless Bridal Makeup Package take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5cabc0c3-5d04-4325-893e-719fb06c149c</t>
+          <t>38b97afd-5409-4155-835d-7d2beb1770eb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling Service Variation 3</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Makeup &amp; Styling</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling</t>
+          <t>Premium Airbrush Special Event Makeup</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>999</v>
+        <v>7499</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Ultra-lightweight airbrush foundation application ensuring 16-hour sweat-proof, poreless perfection.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Complete Makeup &amp; Styling Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Premium Airbrush Special Event Makeup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Makeup &amp; Styling Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Makeup &amp; Styling experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Makeup &amp; Styling Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Makeup &amp; Styling tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Makeup &amp; Styling Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Makeup &amp; Styling Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Premium Airbrush Special Event Makeup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.567971+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.567971+00:00</t>
+          <t>[{'answer': 'The session typically takes around 150 minutes.', 'question': 'How long does Premium Airbrush Special Event Makeup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>719047ad-c57d-4d9a-aeb8-a469a4c1897e</t>
+          <t>363575cf-d407-4352-b218-dc69e79a895e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling Service Variation 4</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Makeup &amp; Styling</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling</t>
+          <t>Pre-Wedding Engagement Makeup</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>999</v>
+        <v>5999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Radiant long-stay engagement look with customized foundation matching, shimmer eyes, and hair draping.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Complete Makeup &amp; Styling Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Pre-Wedding Engagement Makeup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Makeup &amp; Styling Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Makeup &amp; Styling experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Makeup &amp; Styling Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Makeup &amp; Styling tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Makeup &amp; Styling Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Makeup &amp; Styling Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Pre-Wedding Engagement Makeup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.570756+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.570756+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Pre-Wedding Engagement Makeup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13da403a-4cc0-47de-a2d0-c2487adaef18</t>
+          <t>3f55d2dc-3fb4-48b4-b100-c1d48359928d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling Service Variation 5</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Makeup &amp; Styling</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling</t>
+          <t>Saree Draping &amp; Hair Styling Combo</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Professional saree pleating and secure pin-up paired with voluminous curls or traditional braided bun styling.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Complete Makeup &amp; Styling Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Saree Draping &amp; Hair Styling Combo procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Makeup &amp; Styling Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Makeup &amp; Styling experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Makeup &amp; Styling Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Makeup &amp; Styling tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Makeup &amp; Styling Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Makeup &amp; Styling Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Saree Draping &amp; Hair Styling Combo procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.574235+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.574235+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Saree Draping &amp; Hair Styling Combo take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dec9f62f-a4e3-491d-95e5-ef1d548d0981</t>
+          <t>253b8e09-d3b9-4584-916b-bbdd3db67cd3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling Service Variation 6</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Makeup &amp; Styling</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Makeup &amp; Styling</t>
+          <t>Soft Glam Party Makeup</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>999</v>
+        <v>2499</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Elegant evening party makeup including skin prep, custom eyeshadow, false lashes, and smudge-proof lip color.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Complete Makeup &amp; Styling Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Soft Glam Party Makeup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Makeup &amp; Styling Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Makeup &amp; Styling experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Makeup &amp; Styling Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Makeup &amp; Styling tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Makeup &amp; Styling Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Makeup &amp; Styling Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Soft Glam Party Makeup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.577073+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.577073+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Soft Glam Party Makeup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>41cd6220-be9a-456d-9bc8-9f05dc825aa6</t>
+          <t>5117c309-f619-456f-8f26-5dac1f79e03c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 1</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Beard Sculpting &amp; Oil Styling</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>999</v>
+        <v>199</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Razor-sharp beard line trimming, razor edging, and argan oil massage for a polished, sharp look.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Beard Sculpting &amp; Oil Styling procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Beard Sculpting &amp; Oil Styling procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.579769+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.579769+00:00</t>
+          <t>[{'answer': 'The session typically takes around 20 minutes.', 'question': 'How long does Beard Sculpting &amp; Oil Styling take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fcc44f00-04c4-4c27-a61b-fa2320c7df58</t>
+          <t>589aa15f-7225-4e61-b47b-d65bd17c8598</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 10</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Charcoal Face Scrub &amp; Blackhead Extraction</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>999</v>
+        <v>399</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Deep pore exfoliation scrub for men removing nose blackheads, dead skin cells, and daily city pollution layer.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 10 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Charcoal Face Scrub &amp; Blackhead Extraction procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 10 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 10 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 10 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 10 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Charcoal Face Scrub &amp; Blackhead Extraction procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.583394+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.583394+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Charcoal Face Scrub &amp; Blackhead Extraction take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7f124ff8-03ce-4366-81ae-b85cb08688df</t>
+          <t>689d8d79-cdfe-4afd-8d2c-5b015de51b90</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 11</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Executive Groom's Pamper Package</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>999</v>
+        <v>1799</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>All-in-one grooming haircut, beard trim, de-tan facial, and head massage package for groom &amp; groomsmen.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 11 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>["Professional Executive Groom's Pamper Package procedure", 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 11 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 11 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 11 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 11 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>["Complete Executive Groom's Pamper Package procedure", 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.586044+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.586044+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': "How long does Executive Groom's Pamper Package take?"}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7537c8ab-c57b-45e7-b257-84090ac83aa7</t>
+          <t>592641ca-a4ae-4192-8a6c-4bd7914b3abe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 2</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Head Oil Massage &amp; Scalp Relaxation</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>999</v>
+        <v>349</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Traditional warm Mahabhringraj oil head massage stimulating blood circulation and releasing mental stress.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Head Oil Massage &amp; Scalp Relaxation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Head Oil Massage &amp; Scalp Relaxation procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.591004+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.591004+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Head Oil Massage &amp; Scalp Relaxation take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0b139dae-129b-4996-bbdc-dd01d05b43a9</t>
+          <t>5d31b277-768f-4c06-a103-bdd8ec2f3d2a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 3</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Hot Towel Shave &amp; Beard Grooming</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>999</v>
+        <v>249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Classic barbering shave with warm towel pore opening, rich lathering shave, and aftershave balm soothe.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Hot Towel Shave &amp; Beard Grooming procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Hot Towel Shave &amp; Beard Grooming procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.593689+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.593689+00:00</t>
+          <t>[{'answer': 'The session typically takes around 25 minutes.', 'question': 'How long does Hot Towel Shave &amp; Beard Grooming take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>c237a3fc-ee2a-4e8b-95ab-ddcfb1305671</t>
+          <t>4995ea87-05b9-4f89-997a-aff15367d6e5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 4</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Men's Classic Haircut &amp; Wash</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>999</v>
+        <v>299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Precision scissor/clipper haircut tailored to face shape, completed with a scalp wash and blow-dry styling.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>["Professional Men's Classic Haircut &amp; Wash procedure", 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>["Complete Men's Classic Haircut &amp; Wash procedure", 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.596755+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.596755+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': "How long does Men's Classic Haircut &amp; Wash take?"}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>986c14ec-bbad-498e-9d87-d7fc6485bca8</t>
+          <t>5f153195-922b-44e8-b530-55dd22c71cbd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 5</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Men's De-Tan Face Cleanup</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Instant de-tan pack for men exposed to sun and outdoors, clearing forehead and cheek tanning.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>["Professional Men's De-Tan Face Cleanup procedure", 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>["Complete Men's De-Tan Face Cleanup procedure", 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.599872+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.599872+00:00</t>
+          <t>[{'answer': 'The session typically takes around 35 minutes.', 'question': "How long does Men's De-Tan Face Cleanup take?"}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8fb0de98-f428-4def-a02a-81dd26371153</t>
+          <t>67be05ef-0a1d-47bb-9927-f7c7b5e377ff</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 6</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Men's Express Manicure</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Hand nail shaping, cuticle cleanup, hand scrub, and hydrating palm lotion massage.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>["Professional Men's Express Manicure procedure", 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>["Complete Men's Express Manicure procedure", 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.602135+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.602135+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': "How long does Men's Express Manicure take?"}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>787b7704-37a2-4306-90dc-c7edc8f857a6</t>
+          <t>63438b1e-f02d-43c7-a22e-feb1179154e4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 7</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Men's Express Pedicure</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Foot soak, nail trimming, callus scrub, and relaxing foot massage catered specifically for men.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 7 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>["Professional Men's Express Pedicure procedure", 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 7 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 7 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 7 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 7 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>["Complete Men's Express Pedicure procedure", 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.605607+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.605607+00:00</t>
+          <t>[{'answer': 'The session typically takes around 40 minutes.', 'question': "How long does Men's Express Pedicure take?"}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bb694e00-7d40-41c7-84f2-eb3934320fea</t>
+          <t>596a5a73-1a7b-4e99-b55e-66de28e7ed20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 8</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Men's Global Hair Color (Natural Black/Brown)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>100% grey coverage hair coloring using ammonia-free cream dye that leaves hair shiny and natural.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 8 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>["Professional Men's Global Hair Color (Natural Black/Brown) procedure", 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 8 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 8 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 8 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 8 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>["Complete Men's Global Hair Color (Natural Black/Brown) procedure", 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.608461+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.608461+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': "How long does Men's Global Hair Color (Natural Black/Brown) take?"}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>596a5a73-1a7b-4e99-b55e-66de28e7ed20</t>
+          <t>5cabc0c3-5d04-4325-893e-719fb06c149c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Men's Salon Service Variation 9</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Men's Salon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Men's Salon</t>
+          <t>Scalp Detox &amp; Anti-Dandruff Spa</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Tea tree oil scalp treatment dissolving flaky dandruff, soothing itchiness, and strengthening root follicles.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Complete Men's Salon Service Variation 9 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Scalp Detox &amp; Anti-Dandruff Spa procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Men's Salon Service Variation 9 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Men's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Men's Salon Service Variation 9 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Men's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Men's Salon Service Variation 9 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Men's Salon Service Variation 9 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Scalp Detox &amp; Anti-Dandruff Spa procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.610714+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.610714+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Scalp Detox &amp; Anti-Dandruff Spa take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>79bdf09c-0452-4e2b-b479-c8faa8041788</t>
+          <t>6919731b-5173-4307-a782-aca8d6de9579</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 1</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Classic Cut, File &amp; Polish Manicure</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>999</v>
+        <v>399</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Nail shaping, cuticle trimming, hands exfoliation, and high-shine nail polish application.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Classic Cut, File &amp; Polish Manicure procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Classic Cut, File &amp; Polish Manicure procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.613031+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.613031+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Classic Cut, File &amp; Polish Manicure take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bad452d5-0cc0-4490-8331-e850e5d62195</t>
+          <t>787b7704-37a2-4306-90dc-c7edc8f857a6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 10</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Classic Relaxing Foot Pedicure</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Warm foot tub soak, pumice stone heel scrubbing, toe nail grooming, and calf massage.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 10 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Classic Relaxing Foot Pedicure procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 10 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 10 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 10 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 10 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Classic Relaxing Foot Pedicure procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.615474+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.615474+00:00</t>
+          <t>[{'answer': 'The session typically takes around 40 minutes.', 'question': 'How long does Classic Relaxing Foot Pedicure take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>c0c9578f-d3ef-46cd-8861-16c3c92ce428</t>
+          <t>7f124ff8-03ce-4366-81ae-b85cb08688df</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 2</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Crystal Spa Detox Foot Pedicure</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>999</v>
+        <v>1099</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Gelatinous crystal foot bath retaining heat, deeply detoxifying tired feet and softening dry heels.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Crystal Spa Detox Foot Pedicure procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Crystal Spa Detox Foot Pedicure procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.617593+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.617593+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Crystal Spa Detox Foot Pedicure take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>63438b1e-f02d-43c7-a22e-feb1179154e4</t>
+          <t>7537c8ab-c57b-45e7-b257-84090ac83aa7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 3</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Custom Nail Art &amp; Extension Touchup</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Creative nail art designs, ombre gradients, rhinestones, or acrylic extension fill-ins.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Custom Nail Art &amp; Extension Touchup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Custom Nail Art &amp; Extension Touchup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.620611+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.620611+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Custom Nail Art &amp; Extension Touchup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4995ea87-05b9-4f89-997a-aff15367d6e5</t>
+          <t>8fb0de98-f428-4def-a02a-81dd26371153</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 4</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Deluxe De-Tan Mani-Pedi Combo</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>999</v>
+        <v>1299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Combined manicure and pedicure service with specialized anti-tan bleach pack for hands and feet.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Deluxe De-Tan Mani-Pedi Combo procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Deluxe De-Tan Mani-Pedi Combo procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.624048+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.624048+00:00</t>
+          <t>[{'answer': 'The session typically takes around 75 minutes.', 'question': 'How long does Deluxe De-Tan Mani-Pedi Combo take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a2c3d548-e3c5-49cb-b494-0c23719858eb</t>
+          <t>7420713a-26c1-49d8-9ddc-53aa56b9d992</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 5</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Express Cut, File &amp; Polish Change</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>999</v>
+        <v>249</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Quick nail trim, filing into square/round shape, and fresh color polish application.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Express Cut, File &amp; Polish Change procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Express Cut, File &amp; Polish Change procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.627068+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.627068+00:00</t>
+          <t>[{'answer': 'The session typically takes around 20 minutes.', 'question': 'How long does Express Cut, File &amp; Polish Change take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>967a7e89-4bcd-4a26-b787-ac7f05a019d5</t>
+          <t>79bdf09c-0452-4e2b-b479-c8faa8041788</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 6</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Ice Cream Aromatherapy Spa Pedicure</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Fun strawberry/chocolate bath bomb foot soak, sugar scrub exfoliation, and butter cream massage.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Ice Cream Aromatherapy Spa Pedicure procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Ice Cream Aromatherapy Spa Pedicure procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.629555+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.629555+00:00</t>
+          <t>[{'answer': 'The session typically takes around 50 minutes.', 'question': 'How long does Ice Cream Aromatherapy Spa Pedicure take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>025596b2-00b4-490d-9934-19aa2b5e2230</t>
+          <t>8652e4b8-384f-423e-800a-8dcd7695ba66</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 7</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Intensive Heel Peel &amp; Callus Removal</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Targeted chemical heel peel breaking down hard dead callus skin for baby-soft foot soles.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 7 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Intensive Heel Peel &amp; Callus Removal procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 7 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 7 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 7 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 7 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Intensive Heel Peel &amp; Callus Removal procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.631821+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.631821+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Intensive Heel Peel &amp; Callus Removal take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1616f5dc-dc4e-43f9-ac13-d8a3ea223e65</t>
+          <t>73b0b45e-f67d-4cd2-bf02-9727726d0b79</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 8</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Long-Lasting Gel Polish Manicure</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>UV/LED cured gel polish application lasting up to 3 weeks without chipping or dulling.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 8 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Long-Lasting Gel Polish Manicure procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 8 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 8 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 8 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 8 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Long-Lasting Gel Polish Manicure procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.634666+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.634666+00:00</t>
+          <t>[{'answer': 'The session typically takes around 50 minutes.', 'question': 'How long does Long-Lasting Gel Polish Manicure take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>b8fe3316-2ff1-4cb9-a8bb-ea9a8e213be2</t>
+          <t>719047ad-c57d-4d9a-aeb8-a469a4c1897e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure Service Variation 9</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Pedicure &amp; Manicure</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pedicure &amp; Manicure</t>
+          <t>Spa Hydrating &amp; Cuticle Care Manicure</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Luxurious hand mask, deep cuticle nourishment oil massage, and soothing thermal gloves wrap.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>["Complete Pedicure &amp; Manicure Service Variation 9 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Spa Hydrating &amp; Cuticle Care Manicure procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Pedicure &amp; Manicure Service Variation 9 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Pedicure &amp; Manicure experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Pedicure &amp; Manicure Service Variation 9 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Pedicure &amp; Manicure tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Pedicure &amp; Manicure Service Variation 9 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Pedicure &amp; Manicure Service Variation 9 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Spa Hydrating &amp; Cuticle Care Manicure procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.637297+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.637297+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Spa Hydrating &amp; Cuticle Care Manicure take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ffae528d-6975-4aac-9cc2-96092d7ad044</t>
+          <t>967a7e89-4bcd-4a26-b787-ac7f05a019d5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage Service Variation 1</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Spa &amp; Massage</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage</t>
+          <t>Aromatherapy Essential Oil Spa</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>999</v>
+        <v>1699</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Scented lavender and eucalyptus essential oil massage promoting deep mental calm and sleep quality.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>["Complete Spa &amp; Massage Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Aromatherapy Essential Oil Spa procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Spa &amp; Massage Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Spa &amp; Massage experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Spa &amp; Massage Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Spa &amp; Massage tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Spa &amp; Massage Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Spa &amp; Massage Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Aromatherapy Essential Oil Spa procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.641614+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.641614+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Aromatherapy Essential Oil Spa take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>73b0b45e-f67d-4cd2-bf02-9727726d0b79</t>
+          <t>93364c5e-7215-40c6-aa39-0cc02edd4668</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage Service Variation 2</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Spa &amp; Massage</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage</t>
+          <t>Deep Tissue Sports Relief Massage</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>999</v>
+        <v>1899</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Firm targeted pressure targeting chronic muscle knots, lower back tension, and joint stiffness.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>["Complete Spa &amp; Massage Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Deep Tissue Sports Relief Massage procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Spa &amp; Massage Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Spa &amp; Massage experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Spa &amp; Massage Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Spa &amp; Massage tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Spa &amp; Massage Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Spa &amp; Massage Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Deep Tissue Sports Relief Massage procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.644010+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.644010+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Deep Tissue Sports Relief Massage take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5d31b277-768f-4c06-a103-bdd8ec2f3d2a</t>
+          <t>a222a697-5d32-454f-973f-55d19da18838</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage Service Variation 3</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Spa &amp; Massage</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage</t>
+          <t>Express Head, Neck &amp; Shoulder Relief</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Quick desk-worker relief massage focusing on tight neck muscles, upper back, and temples.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>["Complete Spa &amp; Massage Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Express Head, Neck &amp; Shoulder Relief procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Spa &amp; Massage Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Spa &amp; Massage experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Spa &amp; Massage Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Spa &amp; Massage tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Spa &amp; Massage Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Spa &amp; Massage Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Express Head, Neck &amp; Shoulder Relief procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.646459+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.646459+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Express Head, Neck &amp; Shoulder Relief take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>b7340819-ac8b-4ed7-8722-3a6756a44cde</t>
+          <t>91c0c2d6-49a5-44ce-9684-146369687b54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage Service Variation 4</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Spa &amp; Massage</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage</t>
+          <t>Swedish Muscle Relaxation Body Massage</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>999</v>
+        <v>1499</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Classic full-body light to medium pressure massage using long gliding strokes to ease physical fatigue.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>["Complete Spa &amp; Massage Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Swedish Muscle Relaxation Body Massage procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Spa &amp; Massage Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Spa &amp; Massage experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Spa &amp; Massage Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Spa &amp; Massage tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Spa &amp; Massage Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Spa &amp; Massage Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Swedish Muscle Relaxation Body Massage procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.648823+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.648823+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Swedish Muscle Relaxation Body Massage take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>67be05ef-0a1d-47bb-9927-f7c7b5e377ff</t>
+          <t>986c14ec-bbad-498e-9d87-d7fc6485bca8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage Service Variation 5</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Spa &amp; Massage</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage</t>
+          <t>Thai Foot Reflexology Therapy</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>999</v>
+        <v>899</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Pressure-point wooden stick massage on foot soles stimulating internal organ health and leg circulation.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>["Complete Spa &amp; Massage Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Thai Foot Reflexology Therapy procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Spa &amp; Massage Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Spa &amp; Massage experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Spa &amp; Massage Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Spa &amp; Massage tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Spa &amp; Massage Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Spa &amp; Massage Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Thai Foot Reflexology Therapy procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.651364+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.651364+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Thai Foot Reflexology Therapy take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2f23b287-8643-4101-b81d-501a260e8f8e</t>
+          <t>94c94dd3-9320-4b41-90de-774fd27695d7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage Service Variation 6</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Spa &amp; Massage</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Spa &amp; Massage</t>
+          <t>Traditional Ayurvedic Potli Therapy</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>999</v>
+        <v>2199</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Warm herbal poultice filled with medicinal leaves pressed along energy meridians to relieve arthritis and pain.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>["Complete Spa &amp; Massage Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Traditional Ayurvedic Potli Therapy procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Spa &amp; Massage Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Spa &amp; Massage experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Spa &amp; Massage Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Spa &amp; Massage tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Spa &amp; Massage Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Spa &amp; Massage Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Traditional Ayurvedic Potli Therapy procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.653752+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.653752+00:00</t>
+          <t>[{'answer': 'The session typically takes around 75 minutes.', 'question': 'How long does Traditional Ayurvedic Potli Therapy take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a222a697-5d32-454f-973f-55d19da18838</t>
+          <t>b7340819-ac8b-4ed7-8722-3a6756a44cde</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 1</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Ammonia-Free Root Touch-Up</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2630,49 +2821,54 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Precise grey root coverage up to 2 inches using gentle non-damaging ammonia-free dye formula.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 1 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Ammonia-Free Root Touch-Up procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 1 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 1 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 1 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 1 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Ammonia-Free Root Touch-Up procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.657196+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.657196+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Ammonia-Free Root Touch-Up take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>589aa15f-7225-4e61-b47b-d65bd17c8598</t>
+          <t>dec9f62f-a4e3-491d-95e5-ef1d548d0981</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 10</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Deep Conditioning Spa Hair Treatment</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2680,577 +2876,637 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Intensive hair mask application under warm steam, restoring moisture to dry heat-damaged hair ends.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 10 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Deep Conditioning Spa Hair Treatment procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 10 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 10 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 10 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 10 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Deep Conditioning Spa Hair Treatment procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.659903+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.659903+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Deep Conditioning Spa Hair Treatment take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>171399b9-5994-4904-8a3f-0c53cf8e8b66</t>
+          <t>d2fb7f66-07f4-4a50-ae53-25ff1ddbf06b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 11</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>De-Tan Pack &amp; Instant Radiance Cleanup</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>999</v>
+        <v>599</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Quick face cleansing, steam, blackhead removal, and milk &amp; honey de-tan pack.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 11 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional De-Tan Pack &amp; Instant Radiance Cleanup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 11 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 11 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 11 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 11 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete De-Tan Pack &amp; Instant Radiance Cleanup procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.662258+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.662258+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does De-Tan Pack &amp; Instant Radiance Cleanup take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5117c309-f619-456f-8f26-5dac1f79e03c</t>
+          <t>c237a3fc-ee2a-4e8b-95ab-ddcfb1305671</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 12</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Eyebrow &amp; Upper Lip Threading</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Precise cotton thread shaping for clean eyebrow arches and upper lip stray hair removal.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 12 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Eyebrow &amp; Upper Lip Threading procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 12 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 12 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 12 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 12 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Eyebrow &amp; Upper Lip Threading procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.664730+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.664730+00:00</t>
+          <t>[{'answer': 'The session typically takes around 15 minutes.', 'question': 'How long does Eyebrow &amp; Upper Lip Threading take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>592641ca-a4ae-4192-8a6c-4bd7914b3abe</t>
+          <t>c0c9578f-d3ef-46cd-8861-16c3c92ce428</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 13</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Full Arms &amp; Full Legs Waxing (Honey)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Standard warm honey wax removal for arms and legs, finished with soothing aloe vera gel application.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 13 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Full Arms &amp; Full Legs Waxing (Honey) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 13 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 13 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 13 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 13 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Full Arms &amp; Full Legs Waxing (Honey) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.667092+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.667092+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Full Arms &amp; Full Legs Waxing (Honey) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>d2fb7f66-07f4-4a50-ae53-25ff1ddbf06b</t>
+          <t>bb694e00-7d40-41c7-84f2-eb3934320fea</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 2</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Full Body Rica Waxing</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>999</v>
+        <v>1599</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Liposoluble Italian Rica wax for full arms, legs, and underarms giving painless smooth hair removal.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 2 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Full Body Rica Waxing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 2 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 2 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 2 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 2 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Full Body Rica Waxing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.670144+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.670144+00:00</t>
+          <t>[{'answer': 'The session typically takes around 75 minutes.', 'question': 'How long does Full Body Rica Waxing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>689d8d79-cdfe-4afd-8d2c-5b015de51b90</t>
+          <t>b55de068-b024-45bf-8c5f-9ebaccf35767</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 3</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Global Hair Color (L'Oréal / Matrix)</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>999</v>
+        <v>2499</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Full head vibrant hair color transformation using premium salon brands with glossy shine protection.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 3 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>["Professional Global Hair Color (L'Oréal / Matrix) procedure", 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 3 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 3 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 3 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 3 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>["Complete Global Hair Color (L'Oréal / Matrix) procedure", 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.673252+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.673252+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': "How long does Global Hair Color (L'Oréal / Matrix) take?"}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>11eb47da-b142-4b69-9f4e-3507846809cb</t>
+          <t>bad452d5-0cc0-4490-8331-e850e5d62195</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 4</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Hair Rebonding &amp; Straightening</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>999</v>
+        <v>4499</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Permanent sleek straight hair transformation using neutralizer chemical straightening process.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 4 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Hair Rebonding &amp; Straightening procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 4 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 4 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 4 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 4 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Hair Rebonding &amp; Straightening procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.675604+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.675604+00:00</t>
+          <t>[{'answer': 'The session typically takes around 150 minutes.', 'question': 'How long does Hair Rebonding &amp; Straightening take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>164353c2-9cbf-404e-b2e7-22064e69839e</t>
+          <t>b8fe3316-2ff1-4cb9-a8bb-ea9a8e213be2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 5</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Keratin Hair Smoothing Treatment</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>999</v>
+        <v>3999</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Protein-rich keratin infusing treatment eliminating frizzy flyaways and creating silky manageable hair.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 5 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Keratin Hair Smoothing Treatment procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 5 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 5 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 5 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 5 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Keratin Hair Smoothing Treatment procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.678491+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.678491+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Keratin Hair Smoothing Treatment take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>b55de068-b024-45bf-8c5f-9ebaccf35767</t>
+          <t>a2c3d548-e3c5-49cb-b494-0c23719858eb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 6</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Layered Haircut, Wash &amp; Blow Dry</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Stylish layered or feather haircut customized by senior stylist, finished with voluminous blow-dry.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 6 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Layered Haircut, Wash &amp; Blow Dry procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 6 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 6 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 6 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 6 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Layered Haircut, Wash &amp; Blow Dry procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.680570+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.680570+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Layered Haircut, Wash &amp; Blow Dry take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>93364c5e-7215-40c6-aa39-0cc02edd4668</t>
+          <t>fc4d47f1-85e3-4aea-9108-99e66f6528f5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 7</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Organic Fruit Bleach (Face &amp; Neck)</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>999</v>
+        <v>349</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Natural fruit acid bleach lightening facial hair while evening out neck and face discoloration.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 7 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Organic Fruit Bleach (Face &amp; Neck) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 7 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 7 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 7 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 7 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Organic Fruit Bleach (Face &amp; Neck) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.683262+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.683262+00:00</t>
+          <t>[{'answer': 'The session typically takes around 25 minutes.', 'question': 'How long does Organic Fruit Bleach (Face &amp; Neck) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>94c94dd3-9320-4b41-90de-774fd27695d7</t>
+          <t>ffae528d-6975-4aac-9cc2-96092d7ad044</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 8</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Royal Queen Pamper Package</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>999</v>
+        <v>3299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Ultimate head-to-toe package including haircut, facial, hair spa, manicure, and pedicure.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 8 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Royal Queen Pamper Package procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 8 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 8 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 8 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 8 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Royal Queen Pamper Package procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.685501+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.685501+00:00</t>
+          <t>[{'answer': 'The session typically takes around 150 minutes.', 'question': 'How long does Royal Queen Pamper Package take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>363575cf-d407-4352-b218-dc69e79a895e</t>
+          <t>fcc44f00-04c4-4c27-a61b-fa2320c7df58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Women's Salon Service Variation 9</t>
+          <t>1. Beauty, Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1. Beauty, Salon &amp; Spa</t>
+          <t>Women's Salon</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Women's Salon</t>
+          <t>Underarm Tan Removal &amp; Whitening Pack</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>999</v>
+        <v>299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Exfoliating scrub and specialized AHA cream pack targeting dark hyper-pigmented underarms.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>["Complete Women's Salon Service Variation 9 procedure", "Usage of standard tools and materials", "Post-service cleanup", "Expert consultation and advice", "Quality check before handover"]</t>
+          <t>['Professional Underarm Tan Removal &amp; Whitening Pack procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[{"text": "Professional Women's Salon Service Variation 9 services tailored to your needs. Our experts ensure top-tier quality and safety, leaving you completely satisfied with the Women's Salon experience.", "type": "description"}, {"type": "highlights", "items": ["Top quality products and equipment used", "Trained and background-verified professionals", "Hygienic and safe procedures", "100% satisfaction guarantee", "Timely and efficient service delivery"]}, {"type": "excluded_scope", "items": ["Any specialized medical treatments or heavy machinery", "Parts or replacement hardware unless explicitly requested", "Deep structural modifications"]}, {"type": "process_steps", "steps": [{"title": "Initial Assessment", "description": "The professional examines the requirements and plans the service delivery.", "is_key_step": true, "step_number": 1}, {"title": "Preparation &amp; Setup", "description": "Setting up the necessary tools, materials, and safety measures.", "is_key_step": false, "step_number": 2}, {"title": "Core Execution", "description": "Performing the main Women's Salon Service Variation 9 tasks with precision.", "is_key_step": true, "step_number": 3}, {"title": "Finishing Touches", "description": "Applying final finishing touches to ensure perfect results.", "is_key_step": false, "step_number": 4}, {"title": "Cleanup &amp; Handover", "description": "Cleaning the work area and handing over to the customer for approval.", "is_key_step": true, "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Avoid touching the treated area immediately", "Follow the professional's specific post-service advice", "Keep the area dry/ventilated for at least 2 hours"]}, {"type": "tools_materials", "tools": ["Standard Women's Salon tool kit", "Eco-friendly supplies and consumables", "Safety gear (gloves, masks, etc.)", "Sanitization equipment", "Disposable sheets/covers if applicable"], "materials": []}, {"type": "customer_setup", "requirements": ["Ensure a clear working space", "Keep pets and children away from the service area", "Provide access to a power socket and water supply if needed"]}, {"type": "expected_results", "items": ["High quality Women's Salon Service Variation 9 completed successfully", "A clean and safe environment", "Complete customer satisfaction"]}, {"type": "important_notes", "items": ["Service duration may vary based on actual on-site conditions", "Please inform the professional of any allergies or sensitivities beforehand"]}, {"type": "warranty", "details": "7-day service warranty on workmanship", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, all tools are strictly sanitized before and after every session.", "question": "Is the equipment sanitized?"}, {"answer": "Typically between 45 minutes to 2 hours, depending on the specifics.", "question": "How long does Women's Salon Service Variation 9 take?"}, {"answer": "Yes, we only use industry-approved, eco-friendly, and safe products.", "question": "Are the products safe?"}, {"answer": "Yes, basic customizations can be discussed directly with the professional.", "question": "Can I customize the service?"}]}, {"type": "tips", "items": ["Regular maintenance can significantly extend the lifespan of the results.", "Book in advance during weekends and holidays."]}, {"dos": ["Do provide clear instructions before the service begins", "Do inspect the work during the final handover"], "type": "dos_donts", "donts": ["Don't attempt to interrupt the core procedure", "Don't use harsh chemicals on the treated area immediately after"]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Underarm Tan Removal &amp; Whitening Pack procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.690741+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-09-05T14:20:40.690741+00:00</t>
+          <t>[{'answer': 'The session typically takes around 20 minutes.', 'question': 'How long does Underarm Tan Removal &amp; Whitening Pack take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
